--- a/client_evaluation_forms/023_designer_and_assistant_evaluation_form--client_evaluation_forms.xlsx
+++ b/client_evaluation_forms/023_designer_and_assistant_evaluation_form--client_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'below_average',_'label':_'below_average'}</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'below average', 'label': 'Below Average'}</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'below_average',_'label':_'below_average'}</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'below average', 'label': 'Below Average'}</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_at_all',_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'not at all', 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'somewhat',_'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'somewhat', 'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'below_average',_'label':_'below_average'}</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'below average', 'label': 'Below Average'}</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'not_at_all',_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'not at all', 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'somewhat',_'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'somewhat', 'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'almost_always',_'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'almost always', 'label': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'most_of_the_time',_'label':_'most_of_the_time'}</t>
+          <t>most_of_the_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'most of the time', 'label': 'Most of the time'}</t>
+          <t>Most of the time</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'some_of_the_time',_'label':_'some_of_the_time'}</t>
+          <t>some_of_the_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'some of the time', 'label': 'Some of the time'}</t>
+          <t>Some of the time</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'below_average',_'label':_'below_average'}</t>
+          <t>below_average</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'below average', 'label': 'Below Average'}</t>
+          <t>Below Average</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'collaborative',_'label':_'collaborative'}</t>
+          <t>collaborative</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'collaborative', 'label': 'Collaborative'}</t>
+          <t>Collaborative</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'independent',_'label':_'independent'}</t>
+          <t>independent</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'independent', 'label': 'Independent'}</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'autonomous',_'label':_'autonomous'}</t>
+          <t>autonomous</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'autonomous', 'label': 'Autonomous'}</t>
+          <t>Autonomous</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'paused',_'label':_'paused'}</t>
+          <t>paused</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'paused', 'label': 'Paused'}</t>
+          <t>Paused</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'concept',_'label':_'concept'}</t>
+          <t>concept</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'concept', 'label': 'Concept'}</t>
+          <t>Concept</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'design',_'label':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'design', 'label': 'Design'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'testing',_'label':_'testing'}</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'testing', 'label': 'Testing'}</t>
+          <t>Testing</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'launch',_'label':_'launch'}</t>
+          <t>launch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'launch', 'label': 'Launch'}</t>
+          <t>Launch</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'maintenance',_'label':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'maintenance', 'label': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'finished',_'label':_'finished'}</t>
+          <t>finished</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'finished', 'label': 'Finished'}</t>
+          <t>Finished</t>
         </is>
       </c>
     </row>
